--- a/data/Data_&_Files/Data_&_Files_manifest.example.xlsx
+++ b/data/Data_&_Files/Data_&_Files_manifest.example.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t xml:space="preserve">title</t>
   </si>
@@ -32,7 +32,7 @@
     <t xml:space="preserve">Methods</t>
   </si>
   <si>
-    <t xml:space="preserve">Methods.pdf</t>
+    <t xml:space="preserve">methods.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">Description of the experimental and computational methods.</t>
@@ -41,10 +41,22 @@
     <t xml:space="preserve">Documentation</t>
   </si>
   <si>
-    <t xml:space="preserve">Project presentation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project_presentation.pptx</t>
+    <t xml:space="preserve">Analysis report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reports/analysis_report.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full report of the bioinformatic analysis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Results</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project overview</t>
+  </si>
+  <si>
+    <t xml:space="preserve">presentations/project_overview.pptx</t>
   </si>
   <si>
     <t xml:space="preserve">Summary slides of the analysis results.</t>
@@ -53,13 +65,10 @@
     <t xml:space="preserve">Supplementary tables</t>
   </si>
   <si>
-    <t xml:space="preserve">Supplementary_tables.xlsx</t>
+    <t xml:space="preserve">tables/supplementary_tables.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Supplementary result tables.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Results</t>
   </si>
 </sst>
 </file>
@@ -69,7 +78,7 @@
   <numFmts count="1">
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -81,17 +90,28 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -99,14 +119,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -396,21 +422,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="22.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="38.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="60.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="16.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="12.71" hidden="0" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -427,7 +460,7 @@
       <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="3" t="n">
         <v>46023</v>
       </c>
     </row>
@@ -442,26 +475,43 @@
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>46023</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="3" t="n">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>46023</v>
       </c>
     </row>
